--- a/artfynd/A 14372-2025 artfynd.xlsx
+++ b/artfynd/A 14372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131899073</v>
       </c>
       <c r="B2" t="n">
-        <v>79266</v>
+        <v>79269</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131899068</v>
       </c>
       <c r="B3" t="n">
-        <v>79024</v>
+        <v>79027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14372-2025 artfynd.xlsx
+++ b/artfynd/A 14372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131899073</v>
       </c>
       <c r="B2" t="n">
-        <v>79269</v>
+        <v>79274</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131899068</v>
       </c>
       <c r="B3" t="n">
-        <v>79027</v>
+        <v>79032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14372-2025 artfynd.xlsx
+++ b/artfynd/A 14372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131899073</v>
       </c>
       <c r="B2" t="n">
-        <v>79274</v>
+        <v>79276</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131899068</v>
       </c>
       <c r="B3" t="n">
-        <v>79032</v>
+        <v>79034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14372-2025 artfynd.xlsx
+++ b/artfynd/A 14372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131899073</v>
       </c>
       <c r="B2" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131899068</v>
       </c>
       <c r="B3" t="n">
-        <v>79073</v>
+        <v>79075</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14372-2025 artfynd.xlsx
+++ b/artfynd/A 14372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131899073</v>
       </c>
       <c r="B2" t="n">
-        <v>79317</v>
+        <v>79319</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131899068</v>
       </c>
       <c r="B3" t="n">
-        <v>79075</v>
+        <v>79077</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 14372-2025 artfynd.xlsx
+++ b/artfynd/A 14372-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131899073</v>
       </c>
       <c r="B2" t="n">
-        <v>79319</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>131899068</v>
       </c>
       <c r="B3" t="n">
-        <v>79077</v>
+        <v>79085</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
